--- a/data/学生基本信息.xlsx
+++ b/data/学生基本信息.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>赵明</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
